--- a/output/models and plots/rich_model_table.xlsx
+++ b/output/models and plots/rich_model_table.xlsx
@@ -1,62 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10727"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alejo/analysis-alejandro-aldana/output/models and plots/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B5B62F-A7AF-B040-9E3A-6664CD00D8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7180" yWindow="6420" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>formula</t>
-  </si>
-  <si>
-    <t>No_Par</t>
-  </si>
-  <si>
-    <t>logLik</t>
-  </si>
-  <si>
-    <t>AICc</t>
-  </si>
-  <si>
-    <t>Delta_AICc</t>
-  </si>
-  <si>
-    <t>wi_AICc</t>
-  </si>
-  <si>
-    <t>total_abundance ~ bait + canopy + (1 | location)</t>
-  </si>
-  <si>
-    <t>total_abundance ~ bait + canopy + mean_relief + sd_relief + depth +     (1 | location)</t>
-  </si>
-  <si>
-    <t>total_abundance ~ bait + macroalgae + (1 | location)</t>
-  </si>
-  <si>
-    <t>total_abundance ~ macroalgae + scytothalia + canopy + ecklonia +     mean_relief + sd_relief + depth + bait + (1 | location)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -156,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -190,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -225,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -401,111 +350,106 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="90.83203125" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>No_Par</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>logLik</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>AICc</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Delta_AICc</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>wi_AICc</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>6</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>richness ~ bait + macroalgae + (1 | location)</t>
+        </is>
       </c>
       <c r="B2">
         <v>6</v>
       </c>
       <c r="C2">
-        <v>-470.089</v>
+        <v>-297.27</v>
       </c>
       <c r="D2">
-        <v>953.08100000000002</v>
+        <v>607.443</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.88300000000000001</v>
+        <v>0.593</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>7</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>richness ~ bait + canopy + (1 | location)</t>
+        </is>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>-468.99299999999999</v>
+        <v>-298.303</v>
       </c>
       <c r="D3">
-        <v>957.98500000000001</v>
+        <v>609.509</v>
       </c>
       <c r="E3">
-        <v>4.9039999999999999</v>
+        <v>2.066</v>
       </c>
       <c r="F3">
-        <v>7.5999999999999998E-2</v>
+        <v>0.211</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>8</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>richness ~ macroalgae + scytothalia + canopy + ecklonia + mean_relief +     sd_relief + depth + bait + (1 | location)</t>
+        </is>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C4">
-        <v>-473.60399999999998</v>
+        <v>-291.034</v>
       </c>
       <c r="D4">
-        <v>960.11199999999997</v>
+        <v>609.654</v>
       </c>
       <c r="E4">
-        <v>7.0309999999999997</v>
+        <v>2.211</v>
       </c>
       <c r="F4">
-        <v>2.5999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>-466.88</v>
-      </c>
-      <c r="D5">
-        <v>961.346</v>
-      </c>
-      <c r="E5">
-        <v>8.2650000000000006</v>
-      </c>
-      <c r="F5">
-        <v>1.4E-2</v>
+        <v>0.196</v>
       </c>
     </row>
   </sheetData>

--- a/output/models and plots/rich_model_table.xlsx
+++ b/output/models and plots/rich_model_table.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -405,51 +405,73 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.593</v>
+        <v>0.399</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>richness ~ bait + canopy + (1 | location)</t>
+          <t>richness ~ bait + macroalgae + depth + (1 | location)</t>
         </is>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>-298.303</v>
+        <v>-296.315</v>
       </c>
       <c r="D3">
-        <v>609.509</v>
+        <v>607.847</v>
       </c>
       <c r="E3">
-        <v>2.066</v>
+        <v>0.404</v>
       </c>
       <c r="F3">
-        <v>0.211</v>
+        <v>0.326</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>richness ~ bait + canopy + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>-298.303</v>
+      </c>
+      <c r="D4">
+        <v>609.509</v>
+      </c>
+      <c r="E4">
+        <v>2.066</v>
+      </c>
+      <c r="F4">
+        <v>0.142</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>richness ~ macroalgae + scytothalia + canopy + ecklonia + mean_relief +     sd_relief + depth + bait + (1 | location)</t>
         </is>
       </c>
-      <c r="B4">
+      <c r="B5">
         <v>12</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <v>-291.034</v>
       </c>
-      <c r="D4">
+      <c r="D5">
         <v>609.654</v>
       </c>
-      <c r="E4">
+      <c r="E5">
         <v>2.211</v>
       </c>
-      <c r="F4">
-        <v>0.196</v>
+      <c r="F5">
+        <v>0.132</v>
       </c>
     </row>
   </sheetData>

--- a/output/models and plots/rich_model_table.xlsx
+++ b/output/models and plots/rich_model_table.xlsx
@@ -1,21 +1,62 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alejo/analysis-alejandro-aldana/output/models and plots/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{179E9C41-B4FF-DD40-8808-504F88DC5F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="4880" yWindow="3460" windowWidth="19760" windowHeight="10500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>formula</t>
+  </si>
+  <si>
+    <t>No_Par</t>
+  </si>
+  <si>
+    <t>logLik</t>
+  </si>
+  <si>
+    <t>AICc</t>
+  </si>
+  <si>
+    <t>Delta_AICc</t>
+  </si>
+  <si>
+    <t>wi_AICc</t>
+  </si>
+  <si>
+    <t>richness ~ bait + macroalgae + (1 | location)</t>
+  </si>
+  <si>
+    <t>richness ~ bait + macroalgae + depth + (1 | location)</t>
+  </si>
+  <si>
+    <t>richness ~ bait + canopy + (1 | location)</t>
+  </si>
+  <si>
+    <t>richness ~ macroalgae + scytothalia + canopy + ecklonia + mean_relief +     sd_relief + depth + bait + (1 | location)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +104,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +156,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +190,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +225,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,47 +401,36 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="85.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>formula</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>No_Par</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>logLik</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>AICc</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Delta_AICc</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>wi_AICc</t>
-        </is>
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>richness ~ bait + macroalgae + (1 | location)</t>
-        </is>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>6</v>
       </c>
       <c r="B2">
         <v>6</v>
@@ -399,20 +439,18 @@
         <v>-297.27</v>
       </c>
       <c r="D2">
-        <v>607.443</v>
+        <v>607.44299999999998</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.399</v>
+        <v>0.39900000000000002</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>richness ~ bait + macroalgae + depth + (1 | location)</t>
-        </is>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>7</v>
       </c>
       <c r="B3">
         <v>7</v>
@@ -421,20 +459,18 @@
         <v>-296.315</v>
       </c>
       <c r="D3">
-        <v>607.847</v>
+        <v>607.84699999999998</v>
       </c>
       <c r="E3">
-        <v>0.404</v>
+        <v>0.40400000000000003</v>
       </c>
       <c r="F3">
-        <v>0.326</v>
+        <v>0.32600000000000001</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>richness ~ bait + canopy + (1 | location)</t>
-        </is>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>8</v>
       </c>
       <c r="B4">
         <v>6</v>
@@ -443,35 +479,33 @@
         <v>-298.303</v>
       </c>
       <c r="D4">
-        <v>609.509</v>
+        <v>609.50900000000001</v>
       </c>
       <c r="E4">
-        <v>2.066</v>
+        <v>2.0659999999999998</v>
       </c>
       <c r="F4">
-        <v>0.142</v>
+        <v>0.14199999999999999</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>richness ~ macroalgae + scytothalia + canopy + ecklonia + mean_relief +     sd_relief + depth + bait + (1 | location)</t>
-        </is>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>9</v>
       </c>
       <c r="B5">
         <v>12</v>
       </c>
       <c r="C5">
-        <v>-291.034</v>
+        <v>-291.03399999999999</v>
       </c>
       <c r="D5">
         <v>609.654</v>
       </c>
       <c r="E5">
-        <v>2.211</v>
+        <v>2.2109999999999999</v>
       </c>
       <c r="F5">
-        <v>0.132</v>
+        <v>0.13200000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/output/models and plots/rich_model_table.xlsx
+++ b/output/models and plots/rich_model_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alejo/analysis-alejandro-aldana/output/models and plots/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{179E9C41-B4FF-DD40-8808-504F88DC5F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABD9218-7E24-3A45-B672-FEFF90BC36C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4880" yWindow="3460" windowWidth="19760" windowHeight="10500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>formula</t>
   </si>
@@ -32,9 +32,6 @@
   </si>
   <si>
     <t>AICc</t>
-  </si>
-  <si>
-    <t>Delta_AICc</t>
   </si>
   <si>
     <t>wi_AICc</t>
@@ -406,6 +403,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="85.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -422,15 +420,15 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>6</v>
@@ -450,7 +448,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>7</v>
@@ -470,7 +468,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>6</v>
@@ -490,7 +488,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>12</v>

--- a/output/models and plots/rich_model_table.xlsx
+++ b/output/models and plots/rich_model_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alejo/analysis-alejandro-aldana/output/models and plots/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABD9218-7E24-3A45-B672-FEFF90BC36C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B8DBE6-E5D6-904A-AF31-4131FACA3D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
-  <si>
-    <t>formula</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>No_Par</t>
   </si>
@@ -34,9 +31,6 @@
     <t>AICc</t>
   </si>
   <si>
-    <t>wi_AICc</t>
-  </si>
-  <si>
     <t>richness ~ bait + macroalgae + (1 | location)</t>
   </si>
   <si>
@@ -47,6 +41,15 @@
   </si>
   <si>
     <t>richness ~ macroalgae + scytothalia + canopy + ecklonia + mean_relief +     sd_relief + depth + bait + (1 | location)</t>
+  </si>
+  <si>
+    <t>𝛥 AICc</t>
+  </si>
+  <si>
+    <t>AICc w</t>
+  </si>
+  <si>
+    <t>Model</t>
   </si>
 </sst>
 </file>
@@ -408,27 +411,27 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>6</v>
@@ -448,7 +451,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>7</v>
@@ -468,7 +471,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>6</v>
@@ -488,7 +491,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>12</v>

--- a/output/models and plots/rich_model_table.xlsx
+++ b/output/models and plots/rich_model_table.xlsx
@@ -1,62 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10727"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alejo/analysis-alejandro-aldana/output/models and plots/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B8DBE6-E5D6-904A-AF31-4131FACA3D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>No_Par</t>
-  </si>
-  <si>
-    <t>logLik</t>
-  </si>
-  <si>
-    <t>AICc</t>
-  </si>
-  <si>
-    <t>richness ~ bait + macroalgae + (1 | location)</t>
-  </si>
-  <si>
-    <t>richness ~ bait + macroalgae + depth + (1 | location)</t>
-  </si>
-  <si>
-    <t>richness ~ bait + canopy + (1 | location)</t>
-  </si>
-  <si>
-    <t>richness ~ macroalgae + scytothalia + canopy + ecklonia + mean_relief +     sd_relief + depth + bait + (1 | location)</t>
-  </si>
-  <si>
-    <t>𝛥 AICc</t>
-  </si>
-  <si>
-    <t>AICc w</t>
-  </si>
-  <si>
-    <t>Model</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -156,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -190,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -225,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -401,112 +350,1913 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="85.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K57"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>predictors</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AICc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>mR2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>cR2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>RDF</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>n_predictors</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>adjAICc</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>deltaAICc</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>delta_adjAICc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>richness ~ bait + sd_relief + macroalgae + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>sd_relief + macroalgae</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>603.9496942614027</v>
+      </c>
+      <c r="D2">
+        <v>-294.3661514785274</v>
+      </c>
+      <c r="G2">
+        <v>93</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>607.9496942614027</v>
+      </c>
+      <c r="J2">
+        <v>1.4931629791962</v>
+      </c>
+      <c r="K2">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>richness ~ bait + mean_relief + macroalgae + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>mean_relief + macroalgae</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>604.3642339118287</v>
+      </c>
+      <c r="D3">
+        <v>-294.5734213037404</v>
+      </c>
+      <c r="G3">
+        <v>93</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>608.3642339118287</v>
+      </c>
+      <c r="J3">
+        <v>1.907702629622236</v>
+      </c>
+      <c r="K3">
+        <v>0.4145396504260361</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">richness ~ bait + mean_relief + sd_relief + macroalgae + (1 | </t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>mean_relief + sd_relief + macroalgae</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>602.4565312822065</v>
+      </c>
+      <c r="D4">
+        <v>-292.4370568498944</v>
+      </c>
+      <c r="G4">
+        <v>92</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>608.4565312822065</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0.5068370208038004</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    location)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>mean_relief + sd_relief + macroalgae</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>602.4565312822065</v>
+      </c>
+      <c r="D5">
+        <v>-292.4370568498944</v>
+      </c>
+      <c r="G5">
+        <v>92</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>608.4565312822065</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0.5068370208038004</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>richness ~ bait + scytothalia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>scytothalia</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>607.0940384811787</v>
+      </c>
+      <c r="D6">
+        <v>-297.0954063373636</v>
+      </c>
+      <c r="G6">
+        <v>94</v>
+      </c>
+      <c r="H6">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I6">
+        <v>609.0940384811787</v>
+      </c>
+      <c r="J6">
+        <v>4.63750719897223</v>
+      </c>
+      <c r="K6">
+        <v>1.144344219776031</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>richness ~ bait + macroalgae + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>macroalgae</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>607.4432004934531</v>
+      </c>
+      <c r="D7">
+        <v>-297.2699873435008</v>
+      </c>
+      <c r="G7">
+        <v>94</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>609.4432004934531</v>
+      </c>
+      <c r="J7">
+        <v>4.986669211246635</v>
+      </c>
+      <c r="K7">
+        <v>1.493506232050436</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>richness ~ bait + sd_relief + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>sd_relief</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>607.6483924547077</v>
+      </c>
+      <c r="D8">
+        <v>-297.3725833241281</v>
+      </c>
+      <c r="G8">
+        <v>94</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>609.6483924547077</v>
+      </c>
+      <c r="J8">
+        <v>5.191861172501262</v>
+      </c>
+      <c r="K8">
+        <v>1.698698193305063</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>richness ~ bait + sd_relief + macroalgae + ecklonia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sd_relief + macroalgae + ecklonia</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>603.8201583820676</v>
+      </c>
+      <c r="D9">
+        <v>-293.118870399825</v>
+      </c>
+      <c r="G9">
+        <v>92</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+      <c r="I9">
+        <v>609.8201583820676</v>
+      </c>
+      <c r="J9">
+        <v>1.363627099861105</v>
+      </c>
+      <c r="K9">
+        <v>1.870464120664906</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>richness ~ bait + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>609.9020503786988</v>
+      </c>
+      <c r="D10">
+        <v>-299.6318762531792</v>
+      </c>
+      <c r="G10">
+        <v>95</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>609.9020503786988</v>
+      </c>
+      <c r="J10">
+        <v>7.445519096492376</v>
+      </c>
+      <c r="K10">
+        <v>1.952356117296176</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>richness ~ bait + sd_relief + scytothalia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>sd_relief + scytothalia</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>606.2076503738581</v>
+      </c>
+      <c r="D11">
+        <v>-295.4951295347551</v>
+      </c>
+      <c r="G11">
+        <v>93</v>
+      </c>
+      <c r="H11">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
-        <v>6</v>
-      </c>
-      <c r="C2">
-        <v>-297.27</v>
-      </c>
-      <c r="D2">
-        <v>607.44299999999998</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0.39900000000000002</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>-296.315</v>
-      </c>
-      <c r="D3">
-        <v>607.84699999999998</v>
-      </c>
-      <c r="E3">
-        <v>0.40400000000000003</v>
-      </c>
-      <c r="F3">
-        <v>0.32600000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>6</v>
-      </c>
-      <c r="C4">
-        <v>-298.303</v>
-      </c>
-      <c r="D4">
-        <v>609.50900000000001</v>
-      </c>
-      <c r="E4">
-        <v>2.0659999999999998</v>
-      </c>
-      <c r="F4">
-        <v>0.14199999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>-291.03399999999999</v>
-      </c>
-      <c r="D5">
-        <v>609.654</v>
-      </c>
-      <c r="E5">
-        <v>2.2109999999999999</v>
-      </c>
-      <c r="F5">
-        <v>0.13200000000000001</v>
+      <c r="I11">
+        <v>610.2076503738581</v>
+      </c>
+      <c r="J11">
+        <v>3.751119091651617</v>
+      </c>
+      <c r="K11">
+        <v>2.257956112455417</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>richness ~ bait + macroalgae + ecklonia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>macroalgae + ecklonia</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>606.59173698939</v>
+      </c>
+      <c r="D12">
+        <v>-295.6871728425211</v>
+      </c>
+      <c r="G12">
+        <v>93</v>
+      </c>
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12">
+        <v>610.59173698939</v>
+      </c>
+      <c r="J12">
+        <v>4.135205707183559</v>
+      </c>
+      <c r="K12">
+        <v>2.642042727987359</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">richness ~ bait + mean_relief + macroalgae + ecklonia + (1 | </t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>mean_relief + macroalgae + ecklonia</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>604.6187284144337</v>
+      </c>
+      <c r="D13">
+        <v>-293.518155416008</v>
+      </c>
+      <c r="G13">
+        <v>92</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="I13">
+        <v>610.6187284144337</v>
+      </c>
+      <c r="J13">
+        <v>2.16219713222722</v>
+      </c>
+      <c r="K13">
+        <v>2.669034153031021</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    location)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>mean_relief + macroalgae + ecklonia</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>604.6187284144337</v>
+      </c>
+      <c r="D14">
+        <v>-293.518155416008</v>
+      </c>
+      <c r="G14">
+        <v>92</v>
+      </c>
+      <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14">
+        <v>610.6187284144337</v>
+      </c>
+      <c r="J14">
+        <v>2.16219713222722</v>
+      </c>
+      <c r="K14">
+        <v>2.669034153031021</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>richness ~ bait + mean_relief + scytothalia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>mean_relief + scytothalia</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>606.6606899588121</v>
+      </c>
+      <c r="D15">
+        <v>-295.7216493272321</v>
+      </c>
+      <c r="G15">
+        <v>93</v>
+      </c>
+      <c r="H15">
+        <v>2</v>
+      </c>
+      <c r="I15">
+        <v>610.6606899588121</v>
+      </c>
+      <c r="J15">
+        <v>4.20415867660563</v>
+      </c>
+      <c r="K15">
+        <v>2.71099569740943</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>richness ~ bait + depth + mean_relief + macroalgae + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>depth + mean_relief + macroalgae</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>604.7008043367097</v>
+      </c>
+      <c r="D16">
+        <v>-293.559193377146</v>
+      </c>
+      <c r="G16">
+        <v>92</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
+      </c>
+      <c r="I16">
+        <v>610.7008043367097</v>
+      </c>
+      <c r="J16">
+        <v>2.244273054503196</v>
+      </c>
+      <c r="K16">
+        <v>2.751110075306997</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">richness ~ bait + mean_relief + scytothalia + macroalgae + (1 | </t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>mean_relief + scytothalia + macroalgae</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>605.2337323909916</v>
+      </c>
+      <c r="D17">
+        <v>-293.825657404287</v>
+      </c>
+      <c r="G17">
+        <v>92</v>
+      </c>
+      <c r="H17">
+        <v>3</v>
+      </c>
+      <c r="I17">
+        <v>611.2337323909916</v>
+      </c>
+      <c r="J17">
+        <v>2.777201108785107</v>
+      </c>
+      <c r="K17">
+        <v>3.284038129588907</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    location)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>mean_relief + scytothalia + macroalgae</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>605.2337323909916</v>
+      </c>
+      <c r="D18">
+        <v>-293.825657404287</v>
+      </c>
+      <c r="G18">
+        <v>92</v>
+      </c>
+      <c r="H18">
+        <v>3</v>
+      </c>
+      <c r="I18">
+        <v>611.2337323909916</v>
+      </c>
+      <c r="J18">
+        <v>2.777201108785107</v>
+      </c>
+      <c r="K18">
+        <v>3.284038129588907</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>richness ~ bait + sd_relief + canopy + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>sd_relief + canopy</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>607.3723494024781</v>
+      </c>
+      <c r="D19">
+        <v>-296.0774790490651</v>
+      </c>
+      <c r="G19">
+        <v>93</v>
+      </c>
+      <c r="H19">
+        <v>2</v>
+      </c>
+      <c r="I19">
+        <v>611.3723494024781</v>
+      </c>
+      <c r="J19">
+        <v>4.915818120271638</v>
+      </c>
+      <c r="K19">
+        <v>3.422655141075438</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>richness ~ bait + mean_relief + canopy + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>mean_relief + canopy</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>607.4709144565546</v>
+      </c>
+      <c r="D20">
+        <v>-296.1267615761034</v>
+      </c>
+      <c r="G20">
+        <v>93</v>
+      </c>
+      <c r="H20">
+        <v>2</v>
+      </c>
+      <c r="I20">
+        <v>611.4709144565546</v>
+      </c>
+      <c r="J20">
+        <v>5.014383174348154</v>
+      </c>
+      <c r="K20">
+        <v>3.521220195151955</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>richness ~ bait + canopy + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>canopy</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>609.5089075346531</v>
+      </c>
+      <c r="D21">
+        <v>-298.3028408641007</v>
+      </c>
+      <c r="G21">
+        <v>94</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>611.5089075346531</v>
+      </c>
+      <c r="J21">
+        <v>7.052376252446606</v>
+      </c>
+      <c r="K21">
+        <v>3.559213273250407</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">richness ~ bait + sd_relief + scytothalia + macroalgae + (1 | </t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>sd_relief + scytothalia + macroalgae</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>605.6830471862422</v>
+      </c>
+      <c r="D22">
+        <v>-294.0503148019123</v>
+      </c>
+      <c r="G22">
+        <v>92</v>
+      </c>
+      <c r="H22">
+        <v>3</v>
+      </c>
+      <c r="I22">
+        <v>611.6830471862422</v>
+      </c>
+      <c r="J22">
+        <v>3.22651590403575</v>
+      </c>
+      <c r="K22">
+        <v>3.733352924839551</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    location)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>sd_relief + scytothalia + macroalgae</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>605.6830471862422</v>
+      </c>
+      <c r="D23">
+        <v>-294.0503148019123</v>
+      </c>
+      <c r="G23">
+        <v>92</v>
+      </c>
+      <c r="H23">
+        <v>3</v>
+      </c>
+      <c r="I23">
+        <v>611.6830471862422</v>
+      </c>
+      <c r="J23">
+        <v>3.22651590403575</v>
+      </c>
+      <c r="K23">
+        <v>3.733352924839551</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>richness ~ bait + depth + sd_relief + macroalgae + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>depth + sd_relief + macroalgae</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>605.7159939368873</v>
+      </c>
+      <c r="D24">
+        <v>-294.0667881772349</v>
+      </c>
+      <c r="G24">
+        <v>92</v>
+      </c>
+      <c r="H24">
+        <v>3</v>
+      </c>
+      <c r="I24">
+        <v>611.7159939368873</v>
+      </c>
+      <c r="J24">
+        <v>3.259462654680874</v>
+      </c>
+      <c r="K24">
+        <v>3.766299675484674</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>richness ~ bait + depth + macroalgae + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>depth + macroalgae</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>607.8470909079369</v>
+      </c>
+      <c r="D25">
+        <v>-296.3148498017945</v>
+      </c>
+      <c r="G25">
+        <v>93</v>
+      </c>
+      <c r="H25">
+        <v>2</v>
+      </c>
+      <c r="I25">
+        <v>611.8470909079369</v>
+      </c>
+      <c r="J25">
+        <v>5.390559625730475</v>
+      </c>
+      <c r="K25">
+        <v>3.897396646534276</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>richness ~ bait + scytothalia + macroalgae + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>scytothalia + macroalgae</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>607.9064277552012</v>
+      </c>
+      <c r="D26">
+        <v>-296.3445182254267</v>
+      </c>
+      <c r="G26">
+        <v>93</v>
+      </c>
+      <c r="H26">
+        <v>2</v>
+      </c>
+      <c r="I26">
+        <v>611.9064277552012</v>
+      </c>
+      <c r="J26">
+        <v>5.449896472994737</v>
+      </c>
+      <c r="K26">
+        <v>3.956733493798538</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>richness ~ bait + depth + scytothalia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>depth + scytothalia</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>608.1615388787814</v>
+      </c>
+      <c r="D27">
+        <v>-296.4720737872167</v>
+      </c>
+      <c r="G27">
+        <v>93</v>
+      </c>
+      <c r="H27">
+        <v>2</v>
+      </c>
+      <c r="I27">
+        <v>612.1615388787814</v>
+      </c>
+      <c r="J27">
+        <v>5.705007596574887</v>
+      </c>
+      <c r="K27">
+        <v>4.211844617378688</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>richness ~ bait + mean_relief + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>mean_relief</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>610.4459337993347</v>
+      </c>
+      <c r="D28">
+        <v>-298.7713539964416</v>
+      </c>
+      <c r="G28">
+        <v>94</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>612.4459337993347</v>
+      </c>
+      <c r="J28">
+        <v>7.989402517128269</v>
+      </c>
+      <c r="K28">
+        <v>4.49623953793207</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>richness ~ bait + depth + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>610.7531556468698</v>
+      </c>
+      <c r="D29">
+        <v>-298.9249649202091</v>
+      </c>
+      <c r="G29">
+        <v>94</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>612.7531556468698</v>
+      </c>
+      <c r="J29">
+        <v>8.29662436466333</v>
+      </c>
+      <c r="K29">
+        <v>4.803461385467131</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>richness ~ bait + mean_relief + sd_relief + canopy + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>mean_relief + sd_relief + canopy</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>606.7552939214635</v>
+      </c>
+      <c r="D30">
+        <v>-294.5864381695229</v>
+      </c>
+      <c r="G30">
+        <v>92</v>
+      </c>
+      <c r="H30">
+        <v>3</v>
+      </c>
+      <c r="I30">
+        <v>612.7552939214635</v>
+      </c>
+      <c r="J30">
+        <v>4.298762639257006</v>
+      </c>
+      <c r="K30">
+        <v>4.805599660060807</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">richness ~ bait + mean_relief + sd_relief + scytothalia + (1 | </t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>mean_relief + sd_relief + scytothalia</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>606.8162115250376</v>
+      </c>
+      <c r="D31">
+        <v>-294.61689697131</v>
+      </c>
+      <c r="G31">
+        <v>92</v>
+      </c>
+      <c r="H31">
+        <v>3</v>
+      </c>
+      <c r="I31">
+        <v>612.8162115250376</v>
+      </c>
+      <c r="J31">
+        <v>4.359680242831132</v>
+      </c>
+      <c r="K31">
+        <v>4.866517263634933</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    location)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>mean_relief + sd_relief + scytothalia</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>606.8162115250376</v>
+      </c>
+      <c r="D32">
+        <v>-294.61689697131</v>
+      </c>
+      <c r="G32">
+        <v>92</v>
+      </c>
+      <c r="H32">
+        <v>3</v>
+      </c>
+      <c r="I32">
+        <v>612.8162115250376</v>
+      </c>
+      <c r="J32">
+        <v>4.359680242831132</v>
+      </c>
+      <c r="K32">
+        <v>4.866517263634933</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>richness ~ bait + mean_relief + sd_relief + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>mean_relief + sd_relief</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>609.0861836759286</v>
+      </c>
+      <c r="D33">
+        <v>-296.9343961857904</v>
+      </c>
+      <c r="G33">
+        <v>93</v>
+      </c>
+      <c r="H33">
+        <v>2</v>
+      </c>
+      <c r="I33">
+        <v>613.0861836759286</v>
+      </c>
+      <c r="J33">
+        <v>6.629652393722154</v>
+      </c>
+      <c r="K33">
+        <v>5.136489414525954</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>richness ~ bait + scytothalia + ecklonia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>scytothalia + ecklonia</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>609.3325144875256</v>
+      </c>
+      <c r="D34">
+        <v>-297.0575615915889</v>
+      </c>
+      <c r="G34">
+        <v>93</v>
+      </c>
+      <c r="H34">
+        <v>2</v>
+      </c>
+      <c r="I34">
+        <v>613.3325144875256</v>
+      </c>
+      <c r="J34">
+        <v>6.87598320531913</v>
+      </c>
+      <c r="K34">
+        <v>5.382820226122931</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>richness ~ bait + depth + macroalgae + ecklonia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>depth + macroalgae + ecklonia</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>607.4921341313124</v>
+      </c>
+      <c r="D35">
+        <v>-294.9548582744474</v>
+      </c>
+      <c r="G35">
+        <v>92</v>
+      </c>
+      <c r="H35">
+        <v>3</v>
+      </c>
+      <c r="I35">
+        <v>613.4921341313124</v>
+      </c>
+      <c r="J35">
+        <v>5.035602849105885</v>
+      </c>
+      <c r="K35">
+        <v>5.542439869909686</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>richness ~ bait + depth + sd_relief + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>depth + sd_relief</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>609.54655564184</v>
+      </c>
+      <c r="D36">
+        <v>-297.1645821687461</v>
+      </c>
+      <c r="G36">
+        <v>93</v>
+      </c>
+      <c r="H36">
+        <v>2</v>
+      </c>
+      <c r="I36">
+        <v>613.54655564184</v>
+      </c>
+      <c r="J36">
+        <v>7.090024359633503</v>
+      </c>
+      <c r="K36">
+        <v>5.596861380437304</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>richness ~ bait + depth + mean_relief + scytothalia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>depth + mean_relief + scytothalia</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>607.8503252434833</v>
+      </c>
+      <c r="D37">
+        <v>-295.1339538305328</v>
+      </c>
+      <c r="G37">
+        <v>92</v>
+      </c>
+      <c r="H37">
+        <v>3</v>
+      </c>
+      <c r="I37">
+        <v>613.8503252434833</v>
+      </c>
+      <c r="J37">
+        <v>5.393793961276856</v>
+      </c>
+      <c r="K37">
+        <v>5.900630982080656</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>richness ~ bait + depth + mean_relief + canopy + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>depth + mean_relief + canopy</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>607.8568643234671</v>
+      </c>
+      <c r="D38">
+        <v>-295.1372233705247</v>
+      </c>
+      <c r="G38">
+        <v>92</v>
+      </c>
+      <c r="H38">
+        <v>3</v>
+      </c>
+      <c r="I38">
+        <v>613.8568643234671</v>
+      </c>
+      <c r="J38">
+        <v>5.400333041260637</v>
+      </c>
+      <c r="K38">
+        <v>5.907170062064438</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>richness ~ bait + sd_relief + ecklonia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>sd_relief + ecklonia</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>609.957343703929</v>
+      </c>
+      <c r="D39">
+        <v>-297.3699761997906</v>
+      </c>
+      <c r="G39">
+        <v>93</v>
+      </c>
+      <c r="H39">
+        <v>2</v>
+      </c>
+      <c r="I39">
+        <v>613.957343703929</v>
+      </c>
+      <c r="J39">
+        <v>7.500812421722571</v>
+      </c>
+      <c r="K39">
+        <v>6.007649442526372</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>richness ~ bait + depth + canopy + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>depth + canopy</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>610.0308189817187</v>
+      </c>
+      <c r="D40">
+        <v>-297.4067138386854</v>
+      </c>
+      <c r="G40">
+        <v>93</v>
+      </c>
+      <c r="H40">
+        <v>2</v>
+      </c>
+      <c r="I40">
+        <v>614.0308189817187</v>
+      </c>
+      <c r="J40">
+        <v>7.574287699512183</v>
+      </c>
+      <c r="K40">
+        <v>6.081124720315984</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">richness ~ bait + mean_relief + scytothalia + ecklonia + (1 | </t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>mean_relief + scytothalia + ecklonia</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>608.1098579739424</v>
+      </c>
+      <c r="D41">
+        <v>-295.2637201957624</v>
+      </c>
+      <c r="G41">
+        <v>92</v>
+      </c>
+      <c r="H41">
+        <v>3</v>
+      </c>
+      <c r="I41">
+        <v>614.1098579739424</v>
+      </c>
+      <c r="J41">
+        <v>5.65332669173597</v>
+      </c>
+      <c r="K41">
+        <v>6.16016371253977</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    location)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>mean_relief + scytothalia + ecklonia</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>608.1098579739424</v>
+      </c>
+      <c r="D42">
+        <v>-295.2637201957624</v>
+      </c>
+      <c r="G42">
+        <v>92</v>
+      </c>
+      <c r="H42">
+        <v>3</v>
+      </c>
+      <c r="I42">
+        <v>614.1098579739424</v>
+      </c>
+      <c r="J42">
+        <v>5.65332669173597</v>
+      </c>
+      <c r="K42">
+        <v>6.16016371253977</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>richness ~ bait + ecklonia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ecklonia</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>612.121181438815</v>
+      </c>
+      <c r="D43">
+        <v>-299.6089778161817</v>
+      </c>
+      <c r="G43">
+        <v>94</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43">
+        <v>614.121181438815</v>
+      </c>
+      <c r="J43">
+        <v>9.664650156608559</v>
+      </c>
+      <c r="K43">
+        <v>6.171487177412359</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>richness ~ bait + depth + sd_relief + scytothalia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>depth + sd_relief + scytothalia</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>608.1562998237204</v>
+      </c>
+      <c r="D44">
+        <v>-295.2869411206514</v>
+      </c>
+      <c r="G44">
+        <v>92</v>
+      </c>
+      <c r="H44">
+        <v>3</v>
+      </c>
+      <c r="I44">
+        <v>614.1562998237204</v>
+      </c>
+      <c r="J44">
+        <v>5.69976854151389</v>
+      </c>
+      <c r="K44">
+        <v>6.206605562317691</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>richness ~ bait + sd_relief + scytothalia + ecklonia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>sd_relief + scytothalia + ecklonia</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>608.3347534333292</v>
+      </c>
+      <c r="D45">
+        <v>-295.3761679254558</v>
+      </c>
+      <c r="G45">
+        <v>92</v>
+      </c>
+      <c r="H45">
+        <v>3</v>
+      </c>
+      <c r="I45">
+        <v>614.3347534333292</v>
+      </c>
+      <c r="J45">
+        <v>5.878222151122714</v>
+      </c>
+      <c r="K45">
+        <v>6.385059171926514</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>richness ~ bait + depth + scytothalia + macroalgae + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>depth + scytothalia + macroalgae</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>608.6431140436221</v>
+      </c>
+      <c r="D46">
+        <v>-295.5303482306022</v>
+      </c>
+      <c r="G46">
+        <v>92</v>
+      </c>
+      <c r="H46">
+        <v>3</v>
+      </c>
+      <c r="I46">
+        <v>614.6431140436221</v>
+      </c>
+      <c r="J46">
+        <v>6.186582761415593</v>
+      </c>
+      <c r="K46">
+        <v>6.693419782219394</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">richness ~ bait + scytothalia + macroalgae + ecklonia + (1 | </t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>scytothalia + macroalgae + ecklonia</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>608.9249676085479</v>
+      </c>
+      <c r="D47">
+        <v>-295.6712750130652</v>
+      </c>
+      <c r="G47">
+        <v>92</v>
+      </c>
+      <c r="H47">
+        <v>3</v>
+      </c>
+      <c r="I47">
+        <v>614.9249676085479</v>
+      </c>
+      <c r="J47">
+        <v>6.468436326341475</v>
+      </c>
+      <c r="K47">
+        <v>6.975273347145276</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    location)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>scytothalia + macroalgae + ecklonia</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>608.9249676085479</v>
+      </c>
+      <c r="D48">
+        <v>-295.6712750130652</v>
+      </c>
+      <c r="G48">
+        <v>92</v>
+      </c>
+      <c r="H48">
+        <v>3</v>
+      </c>
+      <c r="I48">
+        <v>614.9249676085479</v>
+      </c>
+      <c r="J48">
+        <v>6.468436326341475</v>
+      </c>
+      <c r="K48">
+        <v>6.975273347145276</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>richness ~ bait + depth + sd_relief + canopy + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>depth + sd_relief + canopy</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>609.1246023678426</v>
+      </c>
+      <c r="D49">
+        <v>-295.7710923927125</v>
+      </c>
+      <c r="G49">
+        <v>92</v>
+      </c>
+      <c r="H49">
+        <v>3</v>
+      </c>
+      <c r="I49">
+        <v>615.1246023678426</v>
+      </c>
+      <c r="J49">
+        <v>6.668071085636143</v>
+      </c>
+      <c r="K49">
+        <v>7.174908106439943</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>richness ~ bait + depth + mean_relief + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>depth + mean_relief</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>611.4009307604168</v>
+      </c>
+      <c r="D50">
+        <v>-298.0917697280345</v>
+      </c>
+      <c r="G50">
+        <v>93</v>
+      </c>
+      <c r="H50">
+        <v>2</v>
+      </c>
+      <c r="I50">
+        <v>615.4009307604168</v>
+      </c>
+      <c r="J50">
+        <v>8.944399478210357</v>
+      </c>
+      <c r="K50">
+        <v>7.451236499014158</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>richness ~ bait + depth + scytothalia + ecklonia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>depth + scytothalia + ecklonia</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>610.3427511618378</v>
+      </c>
+      <c r="D51">
+        <v>-296.3801667897101</v>
+      </c>
+      <c r="G51">
+        <v>92</v>
+      </c>
+      <c r="H51">
+        <v>3</v>
+      </c>
+      <c r="I51">
+        <v>616.3427511618378</v>
+      </c>
+      <c r="J51">
+        <v>7.886219879631312</v>
+      </c>
+      <c r="K51">
+        <v>8.393056900435113</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>richness ~ bait + mean_relief + ecklonia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>mean_relief + ecklonia</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>612.7044406965118</v>
+      </c>
+      <c r="D52">
+        <v>-298.743524696082</v>
+      </c>
+      <c r="G52">
+        <v>93</v>
+      </c>
+      <c r="H52">
+        <v>2</v>
+      </c>
+      <c r="I52">
+        <v>616.7044406965118</v>
+      </c>
+      <c r="J52">
+        <v>10.24790941430535</v>
+      </c>
+      <c r="K52">
+        <v>8.754746435109155</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>richness ~ bait + depth + mean_relief + sd_relief + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>depth + mean_relief + sd_relief</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>610.9858985853319</v>
+      </c>
+      <c r="D53">
+        <v>-296.7017405014572</v>
+      </c>
+      <c r="G53">
+        <v>92</v>
+      </c>
+      <c r="H53">
+        <v>3</v>
+      </c>
+      <c r="I53">
+        <v>616.9858985853319</v>
+      </c>
+      <c r="J53">
+        <v>8.529367303125468</v>
+      </c>
+      <c r="K53">
+        <v>9.036204323929269</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>richness ~ bait + depth + ecklonia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>depth + ecklonia</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>613.0635475551073</v>
+      </c>
+      <c r="D54">
+        <v>-298.9230781253797</v>
+      </c>
+      <c r="G54">
+        <v>93</v>
+      </c>
+      <c r="H54">
+        <v>2</v>
+      </c>
+      <c r="I54">
+        <v>617.0635475551073</v>
+      </c>
+      <c r="J54">
+        <v>10.60701627290086</v>
+      </c>
+      <c r="K54">
+        <v>9.113853293704665</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>richness ~ bait + mean_relief + sd_relief + ecklonia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>mean_relief + sd_relief + ecklonia</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>611.2977624645388</v>
+      </c>
+      <c r="D55">
+        <v>-296.8576724410606</v>
+      </c>
+      <c r="G55">
+        <v>92</v>
+      </c>
+      <c r="H55">
+        <v>3</v>
+      </c>
+      <c r="I55">
+        <v>617.2977624645388</v>
+      </c>
+      <c r="J55">
+        <v>8.841231182332308</v>
+      </c>
+      <c r="K55">
+        <v>9.348068203136108</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>richness ~ bait + depth + sd_relief + ecklonia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>depth + sd_relief + ecklonia</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>611.8938761515082</v>
+      </c>
+      <c r="D56">
+        <v>-297.1557292845453</v>
+      </c>
+      <c r="G56">
+        <v>92</v>
+      </c>
+      <c r="H56">
+        <v>3</v>
+      </c>
+      <c r="I56">
+        <v>617.8938761515082</v>
+      </c>
+      <c r="J56">
+        <v>9.437344869301683</v>
+      </c>
+      <c r="K56">
+        <v>9.944181890105483</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>richness ~ bait + depth + mean_relief + ecklonia + (1 | location)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>depth + mean_relief + ecklonia</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>613.6083075852588</v>
+      </c>
+      <c r="D57">
+        <v>-298.0129450014206</v>
+      </c>
+      <c r="G57">
+        <v>92</v>
+      </c>
+      <c r="H57">
+        <v>3</v>
+      </c>
+      <c r="I57">
+        <v>619.6083075852588</v>
+      </c>
+      <c r="J57">
+        <v>11.15177630305232</v>
+      </c>
+      <c r="K57">
+        <v>11.65861332385612</v>
       </c>
     </row>
   </sheetData>
